--- a/artfynd/A 31441-2026 artfynd.xlsx
+++ b/artfynd/A 31441-2026 artfynd.xlsx
@@ -788,7 +788,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Karl Hammar</t>
+          <t>Karl Hammar, Hans Bucht</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -908,7 +908,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Karl Hammar</t>
+          <t>Karl Hammar, Hans Bucht</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 31441-2026 artfynd.xlsx
+++ b/artfynd/A 31441-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137421994</v>
       </c>
       <c r="B2" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>137421997</v>
       </c>
       <c r="B3" t="n">
-        <v>58696</v>
+        <v>58699</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
